--- a/서버정보/20260708_리소스배포_개발.xlsx
+++ b/서버정보/20260708_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A01280-EF02-48B9-B7CB-8CC31E8B1636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FC9F94-0CB1-4F93-B108-81A331053F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1961,10 +1961,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-d-bdp-ext-vnet</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1974,6 +1970,10 @@
   </si>
   <si>
     <t>hazr-d-com-esnap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8369,7 +8369,7 @@
         <v>23</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>381</v>
@@ -8659,7 +8659,7 @@
         <v>377</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="O52" s="1" t="str">
         <f t="shared" si="6"/>
@@ -8747,7 +8747,7 @@
         <v>377</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="O53" s="1" t="str">
         <f t="shared" si="6"/>
@@ -11483,7 +11483,7 @@
         <v>23</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G49" s="17" t="str">
         <f t="shared" si="2"/>
@@ -14207,7 +14207,7 @@
         <v>160</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J66" s="17" t="s">
         <v>50</v>
@@ -14317,7 +14317,7 @@
         <v>49</v>
       </c>
       <c r="G69" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H69" s="32" t="s">
         <v>78</v>
@@ -14355,7 +14355,7 @@
         <v>49</v>
       </c>
       <c r="G70" s="34" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H70" s="34" t="s">
         <v>127</v>
@@ -14392,6 +14392,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -14535,15 +14544,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
@@ -14561,6 +14561,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14576,12 +14584,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>